--- a/cvocd_banana/cvb_bom.xlsx
+++ b/cvocd_banana/cvb_bom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\cvocd.a\cvocd_banana\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E834540A-E505-4868-B935-A86EA82013BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00B9C28-E884-4202-B9EA-D4676183CDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8670" yWindow="-135" windowWidth="20115" windowHeight="15330" xr2:uid="{2C8AAADC-D111-4438-BA7C-E72327EBC990}"/>
+    <workbookView xWindow="810" yWindow="75" windowWidth="19665" windowHeight="14925" xr2:uid="{2C8AAADC-D111-4438-BA7C-E72327EBC990}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="86">
   <si>
     <t>PUSH BUTTON</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Designation</t>
   </si>
   <si>
-    <t>R_0805_2012Metric</t>
-  </si>
-  <si>
     <t>1k</t>
   </si>
   <si>
@@ -290,14 +287,20 @@
     <t>100uF</t>
   </si>
   <si>
-    <t>SWITCH ELEC</t>
+    <t>Spacer</t>
+  </si>
+  <si>
+    <t>M3 20mm F/F</t>
+  </si>
+  <si>
+    <t>per unit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,13 +316,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -334,9 +350,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -671,17 +690,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41DCA404-31BB-4D1D-8DCE-A1B2F31617CC}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="58.5703125" customWidth="1"/>
-    <col min="2" max="2" width="33.28515625" customWidth="1"/>
+    <col min="1" max="1" width="120.7109375" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" customWidth="1"/>
     <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" customWidth="1"/>
     <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -697,151 +717,184 @@
       <c r="F1" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2">
+      <c r="H1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2">
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2">
         <f>$F$1*D2</f>
         <v>600</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G2" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="H2" s="2">
+        <f>D2*G2</f>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3">
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F33" si="0">$F$1*D3</f>
+        <f t="shared" ref="F3:F34" si="0">$F$1*D3</f>
         <v>200</v>
       </c>
       <c r="G3">
         <v>0.43</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="H3">
+        <f t="shared" ref="H3:H34" si="1">D3*G3</f>
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F4">
+      <c r="E4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" s="2">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="2">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6">
+      <c r="G5">
+        <v>0.2</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>2.4000000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="3">
         <v>4</v>
       </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6">
+      <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="3">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="3">
         <v>0.68</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7">
+      <c r="H6" s="3">
+        <f t="shared" si="1"/>
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="3">
         <v>4</v>
       </c>
-      <c r="E7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7">
+      <c r="E7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="3">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="3">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="3">
+        <f t="shared" si="1"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
@@ -850,470 +903,638 @@
       <c r="G8">
         <v>0.09</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>0.44999999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="3">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.68</v>
+      </c>
+      <c r="H9" s="3">
+        <f t="shared" si="1"/>
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="3">
+        <v>12</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="3">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="H10" s="3">
+        <f t="shared" si="1"/>
+        <v>7.8000000000000007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="G9">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B11" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D10">
+      <c r="D11" s="4">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="4">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="H11" s="4">
+        <f t="shared" si="1"/>
+        <v>0.89999999999999991</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="H12" s="4">
+        <f t="shared" si="1"/>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="0"/>
-        <v>600</v>
-      </c>
-      <c r="G10">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>150</v>
-      </c>
-      <c r="G11">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="G12">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="B13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="2">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.23</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="2">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="G13">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="G14">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>69</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="G15">
+      <c r="B15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="4">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G15" s="4">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="H15" s="4">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F16">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="G16">
-        <v>0.28999999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="G17">
+      <c r="F17" s="2">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G17" s="2">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17" s="2">
+        <f t="shared" si="1"/>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18">
         <v>17</v>
       </c>
       <c r="E18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="G18">
+        <v>0.06</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G19">
+        <v>0.06</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
         <v>36</v>
       </c>
-      <c r="F18">
-        <f t="shared" si="0"/>
-        <v>850</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>37</v>
-      </c>
       <c r="F20">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="G20">
+        <v>0.06</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.78</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" si="1"/>
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="H23" s="3">
+        <f t="shared" si="1"/>
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" s="2">
+        <v>4</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D24">
-        <v>4</v>
-      </c>
-      <c r="E24" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24">
+      <c r="F24" s="2">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="2">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24" s="2">
+        <f t="shared" si="1"/>
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D25">
         <v>31</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <f t="shared" si="0"/>
         <v>1550</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="G25">
+        <v>0.01</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="2">
+        <v>4</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B26" t="s">
+      <c r="F26" s="2">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="H26" s="2">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="2">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="H27" s="2">
+        <f t="shared" si="1"/>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="2">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="H28" s="2">
+        <f t="shared" si="1"/>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="2">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="H29" s="2">
+        <f t="shared" si="1"/>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="2">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="H30" s="2">
+        <f t="shared" si="1"/>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D26">
-        <v>4</v>
-      </c>
-      <c r="E26" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="0"/>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="B31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F31" s="2">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="H31" s="2">
+        <f t="shared" si="1"/>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="3">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="H32" s="3">
+        <f t="shared" si="1"/>
+        <v>2.8499999999999996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="3">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="H33" s="3">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34" s="3">
         <v>6</v>
       </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32">
-        <v>3</v>
-      </c>
-      <c r="E32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32">
-        <f t="shared" si="0"/>
-        <v>150</v>
-      </c>
-      <c r="G32">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33" t="s">
-        <v>20</v>
-      </c>
-      <c r="F33">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="G33">
-        <v>0.65</v>
+      <c r="F34" s="3">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="H34" s="3">
+        <f t="shared" si="1"/>
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H35" s="3">
+        <f>SUM(H2:H34)</f>
+        <v>27.410000000000004</v>
       </c>
     </row>
   </sheetData>
